--- a/26-27/Invoice 26-27/23 BK023 Sept AA STONE INVESTMENT TRADING COMPANY (VK) Absolute Long Hand Polish (RJSL)M/measurement sheet - 19-09-26 Absolute black Long Hand Polish (M).xlsx
+++ b/26-27/Invoice 26-27/23 BK023 Sept AA STONE INVESTMENT TRADING COMPANY (VK) Absolute Long Hand Polish (RJSL)M/measurement sheet - 19-09-26 Absolute black Long Hand Polish (M).xlsx
@@ -748,39 +748,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -853,6 +820,39 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,7 +885,7 @@
         <xdr:cNvPr id="2" name="image1.png" title="Image">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1126,26 +1126,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
@@ -1158,64 +1158,64 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="A5" s="75"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="51"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
+      <c r="A8" s="75"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="51"/>
+      <c r="B9" s="75"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1227,11 +1227,11 @@
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="82">
         <f ca="1">TODAY()</f>
         <v>46284</v>
       </c>
-      <c r="C10" s="59"/>
+      <c r="C10" s="83"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -1249,40 +1249,40 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="51"/>
+      <c r="G12" s="75"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="52"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
+      <c r="A13" s="76"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="60" t="s">
+      <c r="F13" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
     </row>
     <row r="14" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="51"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
+      <c r="A14" s="75"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
     </row>
     <row r="15" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
@@ -1305,28 +1305,28 @@
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="69" t="s">
+      <c r="A17" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="70"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="71"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
       <c r="E17" s="11"/>
-      <c r="F17" s="69" t="s">
+      <c r="F17" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="G17" s="70"/>
-      <c r="H17" s="71"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="60"/>
     </row>
     <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="72"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="74"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="12"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="74"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="63"/>
     </row>
     <row r="19" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
@@ -8370,19 +8370,19 @@
       </c>
     </row>
     <row r="265" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="82" t="s">
+      <c r="A265" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B265" s="83"/>
-      <c r="C265" s="84"/>
+      <c r="B265" s="72"/>
+      <c r="C265" s="73"/>
       <c r="D265" s="43">
         <f>SUM(D21:D264)</f>
         <v>476.23810000000003</v>
       </c>
-      <c r="F265" s="80" t="s">
+      <c r="F265" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="G265" s="81"/>
+      <c r="G265" s="70"/>
       <c r="H265" s="43">
         <f>SUM(H21:H264)</f>
         <v>435.03860000000071</v>
@@ -8401,11 +8401,11 @@
       <c r="A267" s="4"/>
       <c r="B267" s="2"/>
       <c r="C267" s="32"/>
-      <c r="D267" s="63" t="s">
+      <c r="D267" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="E267" s="64"/>
-      <c r="F267" s="65"/>
+      <c r="E267" s="53"/>
+      <c r="F267" s="54"/>
       <c r="G267" s="8"/>
       <c r="H267" s="8"/>
     </row>
@@ -8413,9 +8413,9 @@
       <c r="A268" s="4"/>
       <c r="B268" s="2"/>
       <c r="C268" s="32"/>
-      <c r="D268" s="66"/>
-      <c r="E268" s="67"/>
-      <c r="F268" s="68"/>
+      <c r="D268" s="55"/>
+      <c r="E268" s="56"/>
+      <c r="F268" s="57"/>
       <c r="G268" s="8"/>
       <c r="H268" s="8"/>
     </row>
@@ -8423,10 +8423,10 @@
       <c r="A269" s="4"/>
       <c r="B269" s="2"/>
       <c r="C269" s="32"/>
-      <c r="D269" s="76" t="s">
+      <c r="D269" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="E269" s="77"/>
+      <c r="E269" s="66"/>
       <c r="F269" s="9"/>
       <c r="G269" s="32"/>
       <c r="H269" s="8"/>
@@ -8435,10 +8435,10 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="2"/>
-      <c r="D270" s="78" t="s">
+      <c r="D270" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="E270" s="79"/>
+      <c r="E270" s="68"/>
       <c r="F270" s="10">
         <v>244</v>
       </c>
@@ -8449,10 +8449,10 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="2"/>
-      <c r="D271" s="61" t="s">
+      <c r="D271" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="E271" s="62"/>
+      <c r="E271" s="51"/>
       <c r="F271" s="34">
         <f>D265</f>
         <v>476.23810000000003</v>
@@ -8464,10 +8464,10 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="2"/>
-      <c r="D272" s="61" t="s">
+      <c r="D272" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="E272" s="62"/>
+      <c r="E272" s="51"/>
       <c r="F272" s="34">
         <f>H265</f>
         <v>435.03860000000071</v>
@@ -10057,6 +10057,15 @@
   </sheetData>
   <autoFilter ref="A20:I265"/>
   <mergeCells count="18">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C14"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A4:E5"/>
+    <mergeCell ref="A6:E8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="F13:H14"/>
     <mergeCell ref="D271:E271"/>
     <mergeCell ref="D267:F268"/>
     <mergeCell ref="D272:E272"/>
@@ -10066,15 +10075,6 @@
     <mergeCell ref="D270:E270"/>
     <mergeCell ref="F265:G265"/>
     <mergeCell ref="A265:C265"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C14"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A4:E5"/>
-    <mergeCell ref="A6:E8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="F13:H14"/>
   </mergeCells>
   <pageMargins left="0.68500000000000005" right="0" top="0.25" bottom="0.25" header="0" footer="0"/>
   <pageSetup scale="92" orientation="portrait" r:id="rId1"/>
